--- a/jira_export_2026-07-09.xlsx
+++ b/jira_export_2026-07-09.xlsx
@@ -729,7 +729,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>11,820 €</t>
+          <t>12,225 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -743,7 +743,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -776,7 +776,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>8,681 €</t>
+          <t>9,086 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -942,7 +942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P155"/>
+  <dimension ref="A1:P156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -7941,30 +7941,32 @@
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E101" s="12" t="n">
-        <v/>
+          <t>Commune de CLAMART</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="inlineStr">
+        <is>
+          <t>Migration V2</t>
+        </is>
       </c>
       <c r="F101" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G101" s="12" t="inlineStr">
@@ -7974,35 +7976,35 @@
       </c>
       <c r="H101" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I101" s="12" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J101" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K101" s="12" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L101" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M101" s="12" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N101" s="13" t="n">
-        <v>2812.32</v>
-      </c>
-      <c r="O101" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O101" s="13" t="n">
+        <v>405</v>
       </c>
       <c r="P101" s="13" t="n">
         <v>0</v>
@@ -8011,12 +8013,12 @@
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr">
@@ -8026,13 +8028,11 @@
       </c>
       <c r="D102" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E102" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E102" s="15" t="n">
+        <v/>
       </c>
       <c r="F102" s="15" t="inlineStr">
         <is>
@@ -8051,27 +8051,27 @@
       </c>
       <c r="I102" s="15" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J102" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K102" s="15" t="n">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="L102" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M102" s="15" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N102" s="16" t="n">
-        <v>392.5</v>
+        <v>2812.32</v>
       </c>
       <c r="O102" s="17" t="n">
         <v>0</v>
@@ -8134,16 +8134,16 @@
       </c>
       <c r="L103" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M103" s="12" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N103" s="13" t="n">
-        <v>1556.25</v>
+        <v>392.5</v>
       </c>
       <c r="O103" s="17" t="n">
         <v>0</v>
@@ -8206,16 +8206,16 @@
       </c>
       <c r="L104" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M104" s="15" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N104" s="16" t="n">
-        <v>1790</v>
+        <v>1556.25</v>
       </c>
       <c r="O104" s="17" t="n">
         <v>0</v>
@@ -8278,18 +8278,18 @@
       </c>
       <c r="L105" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M105" s="12" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N105" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O105" s="13" t="n">
+        <v>1790</v>
+      </c>
+      <c r="O105" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P105" s="13" t="n">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="L106" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M106" s="15" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N106" s="16" t="n">
@@ -8371,12 +8371,12 @@
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
@@ -8386,11 +8386,13 @@
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E107" s="12" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E107" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F107" s="12" t="inlineStr">
         <is>
@@ -8404,28 +8406,28 @@
       </c>
       <c r="H107" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I107" s="12" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J107" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K107" s="12" t="n">
-        <v>4.25</v>
+        <v>0.85</v>
       </c>
       <c r="L107" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M107" s="12" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N107" s="13" t="n">
@@ -8441,12 +8443,12 @@
     <row r="108">
       <c r="A108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">
@@ -8456,7 +8458,7 @@
       </c>
       <c r="D108" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
         </is>
       </c>
       <c r="E108" s="15" t="n">
@@ -8474,34 +8476,34 @@
       </c>
       <c r="H108" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I108" s="15" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J108" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K108" s="15" t="n">
-        <v>2.5</v>
+        <v>4.25</v>
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-27642</t>
         </is>
       </c>
       <c r="M108" s="15" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00143935</t>
         </is>
       </c>
       <c r="N108" s="16" t="n">
-        <v>732</v>
-      </c>
-      <c r="O108" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P108" s="16" t="n">
@@ -8511,12 +8513,12 @@
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26831</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
@@ -8526,38 +8528,52 @@
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>CD74</t>
-        </is>
-      </c>
-      <c r="E109" s="12" t="inlineStr">
-        <is>
-          <t>MAJ carto</t>
-        </is>
-      </c>
-      <c r="F109" s="12" t="inlineStr"/>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="n">
+        <v/>
+      </c>
+      <c r="F109" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="H109" s="12" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H109" s="12" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I109" s="12" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J109" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K109" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L109" s="12" t="inlineStr"/>
-      <c r="M109" s="12" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="L109" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27557</t>
+        </is>
+      </c>
+      <c r="M109" s="12" t="inlineStr">
+        <is>
+          <t>00144532</t>
+        </is>
+      </c>
       <c r="N109" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O109" s="13" t="n">
+        <v>732</v>
+      </c>
+      <c r="O109" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P109" s="13" t="n">
@@ -8567,12 +8583,12 @@
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-26831</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
         </is>
       </c>
       <c r="C110" s="15" t="inlineStr">
@@ -8582,48 +8598,34 @@
       </c>
       <c r="D110" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
-        </is>
-      </c>
-      <c r="E110" s="15" t="n">
-        <v/>
-      </c>
-      <c r="F110" s="15" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+          <t>CD74</t>
+        </is>
+      </c>
+      <c r="E110" s="15" t="inlineStr">
+        <is>
+          <t>MAJ carto</t>
+        </is>
+      </c>
+      <c r="F110" s="15" t="inlineStr"/>
       <c r="G110" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H110" s="15" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="H110" s="15" t="inlineStr"/>
       <c r="I110" s="15" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="J110" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K110" s="15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L110" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-26814</t>
-        </is>
-      </c>
-      <c r="M110" s="15" t="inlineStr">
-        <is>
-          <t>00142941</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L110" s="15" t="inlineStr"/>
+      <c r="M110" s="15" t="inlineStr"/>
       <c r="N110" s="16" t="n">
         <v>0</v>
       </c>
@@ -8637,28 +8639,26 @@
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26782</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
-        </is>
-      </c>
-      <c r="E111" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement LiEx</t>
-        </is>
+          <t>VILLE DE VILLEJUIF</t>
+        </is>
+      </c>
+      <c r="E111" s="12" t="n">
+        <v/>
       </c>
       <c r="F111" s="12" t="inlineStr">
         <is>
@@ -8672,28 +8672,28 @@
       </c>
       <c r="H111" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I111" s="12" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J111" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K111" s="12" t="n">
-        <v>6.75</v>
+        <v>1.25</v>
       </c>
       <c r="L111" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-26783</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M111" s="12" t="inlineStr">
         <is>
-          <t>00142659</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N111" s="13" t="n">
@@ -8709,26 +8709,28 @@
     <row r="112">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-26782</t>
         </is>
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
         </is>
       </c>
       <c r="C112" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D112" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
-        </is>
-      </c>
-      <c r="E112" s="15" t="n">
-        <v/>
+          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
+        </is>
+      </c>
+      <c r="E112" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement LiEx</t>
+        </is>
       </c>
       <c r="F112" s="15" t="inlineStr">
         <is>
@@ -8747,29 +8749,29 @@
       </c>
       <c r="I112" s="15" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J112" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K112" s="15" t="n">
-        <v>1</v>
+        <v>6.75</v>
       </c>
       <c r="L112" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-26783</t>
         </is>
       </c>
       <c r="M112" s="15" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00142659</t>
         </is>
       </c>
       <c r="N112" s="16" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O112" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P112" s="16" t="n">
@@ -8779,12 +8781,12 @@
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24765</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>[COLOMBES] -  Litteralis - Interface Pastell</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
@@ -8794,7 +8796,7 @@
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE COLOMBES - DSIO</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E113" s="12" t="n">
@@ -8812,34 +8814,34 @@
       </c>
       <c r="H113" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I113" s="12" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J113" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K113" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L113" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28062</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M113" s="12" t="inlineStr">
         <is>
-          <t>500768</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N113" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O113" s="13" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O113" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P113" s="13" t="n">
@@ -8849,22 +8851,22 @@
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24426</t>
+          <t>PDMDEP-24765</t>
         </is>
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>[DRANCY] - Migration STD vers Exp</t>
+          <t>[COLOMBES] -  Litteralis - Interface Pastell</t>
         </is>
       </c>
       <c r="C114" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D114" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE DRANCY</t>
+          <t>VILLE DE COLOMBES - DSIO</t>
         </is>
       </c>
       <c r="E114" s="15" t="n">
@@ -8887,23 +8889,23 @@
       </c>
       <c r="I114" s="15" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="J114" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K114" s="15" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="L114" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27028</t>
+          <t>PDMDEP-28062</t>
         </is>
       </c>
       <c r="M114" s="15" t="inlineStr">
         <is>
-          <t>500950</t>
+          <t>500768</t>
         </is>
       </c>
       <c r="N114" s="16" t="n">
@@ -8919,12 +8921,12 @@
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
@@ -8934,7 +8936,7 @@
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
+          <t>VILLE DE DRANCY</t>
         </is>
       </c>
       <c r="E115" s="12" t="n">
@@ -8952,28 +8954,28 @@
       </c>
       <c r="H115" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I115" s="12" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J115" s="12" t="n">
         <v>10</v>
       </c>
       <c r="K115" s="12" t="n">
-        <v>1.38</v>
+        <v>0.25</v>
       </c>
       <c r="L115" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27996</t>
+          <t>PDMDEP-27028</t>
         </is>
       </c>
       <c r="M115" s="12" t="inlineStr">
         <is>
-          <t>501219</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="N115" s="13" t="n">
@@ -9038,12 +9040,12 @@
       </c>
       <c r="L116" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27995</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M116" s="15" t="inlineStr">
         <is>
-          <t>501218</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N116" s="16" t="n">
@@ -9059,22 +9061,22 @@
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E117" s="12" t="n">
@@ -9097,29 +9099,29 @@
       </c>
       <c r="I117" s="12" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J117" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K117" s="12" t="n">
-        <v>3.25</v>
+        <v>1.38</v>
       </c>
       <c r="L117" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M117" s="12" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N117" s="13" t="n">
-        <v>2323</v>
-      </c>
-      <c r="O117" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P117" s="13" t="n">
@@ -9129,22 +9131,22 @@
     <row r="118">
       <c r="A118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23486</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- AJOUT BALISE FILIEN</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C118" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E118" s="15" t="n">
@@ -9152,7 +9154,7 @@
       </c>
       <c r="F118" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G118" s="15" t="inlineStr">
@@ -9162,32 +9164,32 @@
       </c>
       <c r="H118" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I118" s="15" t="inlineStr">
         <is>
-          <t>25/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J118" s="15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K118" s="15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="L118" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27493</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M118" s="15" t="inlineStr">
         <is>
-          <t>495699</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N118" s="16" t="n">
-        <v>964.1</v>
+        <v>2323</v>
       </c>
       <c r="O118" s="17" t="n">
         <v>0</v>
@@ -9199,12 +9201,12 @@
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23484</t>
+          <t>PDMDEP-23486</t>
         </is>
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- AJOUT LIEU DE NAISSANCE DANS FILIEN</t>
+          <t>METROPOLE TOULON- AJOUT BALISE FILIEN</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
@@ -9248,19 +9250,19 @@
       </c>
       <c r="L119" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27494</t>
+          <t>PDMDEP-27493</t>
         </is>
       </c>
       <c r="M119" s="12" t="inlineStr">
         <is>
-          <t>495695</t>
+          <t>495699</t>
         </is>
       </c>
       <c r="N119" s="13" t="n">
-        <v>140.4</v>
+        <v>964.1</v>
       </c>
       <c r="O119" s="17" t="n">
-        <v>70.2</v>
+        <v>0</v>
       </c>
       <c r="P119" s="13" t="n">
         <v>0</v>
@@ -9269,22 +9271,22 @@
     <row r="120">
       <c r="A120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-23484</t>
         </is>
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>METROPOLE TOULON- AJOUT LIEU DE NAISSANCE DANS FILIEN</t>
         </is>
       </c>
       <c r="C120" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D120" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E120" s="15" t="n">
@@ -9292,7 +9294,7 @@
       </c>
       <c r="F120" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G120" s="15" t="inlineStr">
@@ -9302,35 +9304,35 @@
       </c>
       <c r="H120" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I120" s="15" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>25/07/2025</t>
         </is>
       </c>
       <c r="J120" s="15" t="n">
         <v>12</v>
       </c>
       <c r="K120" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L120" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-27494</t>
         </is>
       </c>
       <c r="M120" s="15" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>495695</t>
         </is>
       </c>
       <c r="N120" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O120" s="16" t="n">
-        <v>0</v>
+        <v>140.4</v>
+      </c>
+      <c r="O120" s="17" t="n">
+        <v>70.2</v>
       </c>
       <c r="P120" s="16" t="n">
         <v>0</v>
@@ -9339,22 +9341,22 @@
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-22996</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E121" s="12" t="n">
@@ -9372,28 +9374,28 @@
       </c>
       <c r="H121" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I121" s="12" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J121" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K121" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L121" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28051</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M121" s="12" t="inlineStr">
         <is>
-          <t>487190</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N121" s="13" t="n">
@@ -9409,22 +9411,22 @@
     <row r="122">
       <c r="A122" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-22996</t>
         </is>
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
         </is>
       </c>
       <c r="C122" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D122" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E122" s="15" t="n">
@@ -9442,28 +9444,28 @@
       </c>
       <c r="H122" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I122" s="15" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="J122" s="15" t="n">
         <v>12</v>
       </c>
       <c r="K122" s="15" t="n">
-        <v>0.12</v>
+        <v>2</v>
       </c>
       <c r="L122" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-28051</t>
         </is>
       </c>
       <c r="M122" s="15" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>487190</t>
         </is>
       </c>
       <c r="N122" s="16" t="n">
@@ -9528,12 +9530,12 @@
       </c>
       <c r="L123" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M123" s="12" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N123" s="13" t="n">
@@ -9564,7 +9566,7 @@
       </c>
       <c r="D124" s="15" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E124" s="15" t="n">
@@ -9598,12 +9600,12 @@
       </c>
       <c r="L124" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M124" s="15" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N124" s="16" t="n">
@@ -9634,7 +9636,7 @@
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E125" s="12" t="n">
@@ -9668,12 +9670,12 @@
       </c>
       <c r="L125" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M125" s="12" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N125" s="13" t="n">
@@ -9689,12 +9691,12 @@
     <row r="126">
       <c r="A126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22496</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - LITTERALIS Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C126" s="15" t="inlineStr">
@@ -9704,7 +9706,7 @@
       </c>
       <c r="D126" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E126" s="15" t="n">
@@ -9722,28 +9724,28 @@
       </c>
       <c r="H126" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I126" s="15" t="inlineStr">
         <is>
-          <t>23/06/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J126" s="15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K126" s="15" t="n">
-        <v>0.5</v>
+        <v>0.12</v>
       </c>
       <c r="L126" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27371</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M126" s="15" t="inlineStr">
         <is>
-          <t>481817</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N126" s="16" t="n">
@@ -9759,22 +9761,22 @@
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22496</t>
         </is>
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>[VILLEJUIF] - LITTERALIS Pastell</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E127" s="12" t="n">
@@ -9797,23 +9799,23 @@
       </c>
       <c r="I127" s="12" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>23/06/2025</t>
         </is>
       </c>
       <c r="J127" s="12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K127" s="12" t="n">
         <v>0.5</v>
       </c>
       <c r="L127" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27371</t>
         </is>
       </c>
       <c r="M127" s="12" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>481817</t>
         </is>
       </c>
       <c r="N127" s="13" t="n">
@@ -9829,22 +9831,22 @@
     <row r="128">
       <c r="A128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21546</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C128" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D128" s="15" t="inlineStr">
         <is>
-          <t>VILLEURBANNE</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E128" s="15" t="n">
@@ -9852,7 +9854,7 @@
       </c>
       <c r="F128" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G128" s="15" t="inlineStr">
@@ -9867,29 +9869,29 @@
       </c>
       <c r="I128" s="15" t="inlineStr">
         <is>
-          <t>05/05/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J128" s="15" t="n">
         <v>14</v>
       </c>
       <c r="K128" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L128" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28038</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M128" s="15" t="inlineStr">
         <is>
-          <t>478867</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N128" s="16" t="n">
-        <v>482.72</v>
-      </c>
-      <c r="O128" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P128" s="16" t="n">
@@ -9899,22 +9901,22 @@
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21546</t>
         </is>
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>VILLEURBANNE</t>
         </is>
       </c>
       <c r="E129" s="12" t="n">
@@ -9922,7 +9924,7 @@
       </c>
       <c r="F129" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G129" s="12" t="inlineStr">
@@ -9932,34 +9934,34 @@
       </c>
       <c r="H129" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I129" s="12" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="J129" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K129" s="12" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L129" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-28038</t>
         </is>
       </c>
       <c r="M129" s="12" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>478867</t>
         </is>
       </c>
       <c r="N129" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O129" s="13" t="n">
+        <v>482.72</v>
+      </c>
+      <c r="O129" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P129" s="13" t="n">
@@ -9969,22 +9971,22 @@
     <row r="130">
       <c r="A130" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C130" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D130" s="15" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E130" s="15" t="n">
@@ -10002,34 +10004,34 @@
       </c>
       <c r="H130" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I130" s="15" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J130" s="15" t="n">
         <v>15</v>
       </c>
       <c r="K130" s="15" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L130" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M130" s="15" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N130" s="16" t="n">
-        <v>250</v>
-      </c>
-      <c r="O130" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P130" s="16" t="n">
@@ -10039,22 +10041,22 @@
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E131" s="12" t="n">
@@ -10077,27 +10079,27 @@
       </c>
       <c r="I131" s="12" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J131" s="12" t="n">
         <v>15</v>
       </c>
       <c r="K131" s="12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L131" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M131" s="12" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N131" s="13" t="n">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="O131" s="17" t="n">
         <v>0</v>
@@ -10109,22 +10111,22 @@
     <row r="132">
       <c r="A132" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C132" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D132" s="15" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E132" s="15" t="n">
@@ -10140,24 +10142,36 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H132" s="15" t="inlineStr"/>
+      <c r="H132" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I132" s="15" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J132" s="15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K132" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L132" s="15" t="inlineStr"/>
-      <c r="M132" s="15" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L132" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M132" s="15" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
       <c r="N132" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O132" s="16" t="n">
+        <v>230</v>
+      </c>
+      <c r="O132" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P132" s="16" t="n">
@@ -10167,22 +10181,22 @@
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E133" s="12" t="n">
@@ -10198,32 +10212,20 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H133" s="12" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H133" s="12" t="inlineStr"/>
       <c r="I133" s="12" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J133" s="12" t="n">
         <v>16</v>
       </c>
       <c r="K133" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L133" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-28027</t>
-        </is>
-      </c>
-      <c r="M133" s="12" t="inlineStr">
-        <is>
-          <t>470688</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L133" s="12" t="inlineStr"/>
+      <c r="M133" s="12" t="inlineStr"/>
       <c r="N133" s="13" t="n">
         <v>0</v>
       </c>
@@ -10237,12 +10239,12 @@
     <row r="134">
       <c r="A134" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C134" s="15" t="inlineStr">
@@ -10252,7 +10254,7 @@
       </c>
       <c r="D134" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E134" s="15" t="n">
@@ -10270,28 +10272,28 @@
       </c>
       <c r="H134" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I134" s="15" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J134" s="15" t="n">
         <v>16</v>
       </c>
       <c r="K134" s="15" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L134" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M134" s="15" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N134" s="16" t="n">
@@ -10307,12 +10309,12 @@
     <row r="135">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B135" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
@@ -10322,7 +10324,7 @@
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E135" s="12" t="n">
@@ -10340,28 +10342,28 @@
       </c>
       <c r="H135" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I135" s="12" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J135" s="12" t="n">
         <v>16</v>
       </c>
       <c r="K135" s="12" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L135" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M135" s="12" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N135" s="13" t="n">
@@ -10377,12 +10379,12 @@
     <row r="136">
       <c r="A136" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19385</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C136" s="15" t="inlineStr">
@@ -10392,7 +10394,7 @@
       </c>
       <c r="D136" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARCUEIL</t>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
         </is>
       </c>
       <c r="E136" s="15" t="n">
@@ -10415,23 +10417,23 @@
       </c>
       <c r="I136" s="15" t="inlineStr">
         <is>
-          <t>24/02/2025</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J136" s="15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K136" s="15" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L136" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27535</t>
+          <t>PDMDEP-27377</t>
         </is>
       </c>
       <c r="M136" s="15" t="inlineStr">
         <is>
-          <t>465345</t>
+          <t>478048</t>
         </is>
       </c>
       <c r="N136" s="16" t="n">
@@ -10447,12 +10449,12 @@
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-19385</t>
         </is>
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
@@ -10462,7 +10464,7 @@
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>COMMUNE D'ARCUEIL</t>
         </is>
       </c>
       <c r="E137" s="12" t="n">
@@ -10475,7 +10477,7 @@
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H137" s="12" t="inlineStr">
@@ -10485,17 +10487,25 @@
       </c>
       <c r="I137" s="12" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>24/02/2025</t>
         </is>
       </c>
       <c r="J137" s="12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K137" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L137" s="12" t="inlineStr"/>
-      <c r="M137" s="12" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L137" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27535</t>
+        </is>
+      </c>
+      <c r="M137" s="12" t="inlineStr">
+        <is>
+          <t>465345</t>
+        </is>
+      </c>
       <c r="N137" s="13" t="n">
         <v>0</v>
       </c>
@@ -10509,22 +10519,22 @@
     <row r="138">
       <c r="A138" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C138" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D138" s="15" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E138" s="15" t="n">
@@ -10532,44 +10542,36 @@
       </c>
       <c r="F138" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G138" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H138" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I138" s="15" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J138" s="15" t="n">
         <v>19</v>
       </c>
       <c r="K138" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L138" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M138" s="15" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="L138" s="15" t="inlineStr"/>
+      <c r="M138" s="15" t="inlineStr"/>
       <c r="N138" s="16" t="n">
-        <v>240</v>
-      </c>
-      <c r="O138" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P138" s="16" t="n">
@@ -10579,22 +10581,22 @@
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E139" s="12" t="n">
@@ -10602,7 +10604,7 @@
       </c>
       <c r="F139" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G139" s="12" t="inlineStr">
@@ -10612,34 +10614,34 @@
       </c>
       <c r="H139" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I139" s="12" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J139" s="12" t="n">
         <v>19</v>
       </c>
       <c r="K139" s="12" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="L139" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34362</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M139" s="12" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N139" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O139" s="13" t="n">
+        <v>240</v>
+      </c>
+      <c r="O139" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P139" s="13" t="n">
@@ -10664,7 +10666,7 @@
       </c>
       <c r="D140" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
       <c r="E140" s="15" t="n">
@@ -10698,7 +10700,7 @@
       </c>
       <c r="L140" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28020</t>
+          <t>PDMDEP-34362</t>
         </is>
       </c>
       <c r="M140" s="15" t="inlineStr">
@@ -10719,22 +10721,22 @@
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-16868</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t>[Limoges] migration placier</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>Limoges</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E141" s="12" t="n">
@@ -10742,32 +10744,40 @@
       </c>
       <c r="F141" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H141" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I141" s="12" t="inlineStr">
         <is>
-          <t>26/09/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J141" s="12" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K141" s="12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L141" s="12" t="inlineStr"/>
-      <c r="M141" s="12" t="inlineStr"/>
+        <v>0.62</v>
+      </c>
+      <c r="L141" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28020</t>
+        </is>
+      </c>
+      <c r="M141" s="12" t="inlineStr">
+        <is>
+          <t>458057</t>
+        </is>
+      </c>
       <c r="N141" s="13" t="n">
         <v>0</v>
       </c>
@@ -10781,22 +10791,22 @@
     <row r="142">
       <c r="A142" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-16868</t>
         </is>
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[Limoges] migration placier</t>
         </is>
       </c>
       <c r="C142" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D142" s="15" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>Limoges</t>
         </is>
       </c>
       <c r="E142" s="15" t="n">
@@ -10804,7 +10814,7 @@
       </c>
       <c r="F142" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G142" s="15" t="inlineStr">
@@ -10814,19 +10824,19 @@
       </c>
       <c r="H142" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I142" s="15" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>26/09/2024</t>
         </is>
       </c>
       <c r="J142" s="15" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K142" s="15" t="n">
-        <v>0.25</v>
+        <v>3.25</v>
       </c>
       <c r="L142" s="15" t="inlineStr"/>
       <c r="M142" s="15" t="inlineStr"/>
@@ -10843,22 +10853,22 @@
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14551</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t>[Perpignan] Interface formulaire</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>[Perpignan]</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E143" s="12" t="n">
@@ -10881,14 +10891,14 @@
       </c>
       <c r="I143" s="12" t="inlineStr">
         <is>
-          <t>14/03/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J143" s="12" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K143" s="12" t="n">
-        <v>1.25</v>
+        <v>0.25</v>
       </c>
       <c r="L143" s="12" t="inlineStr"/>
       <c r="M143" s="12" t="inlineStr"/>
@@ -10905,12 +10915,12 @@
     <row r="144">
       <c r="A144" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14254</t>
+          <t>PDMDEP-14551</t>
         </is>
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
+          <t>[Perpignan] Interface formulaire</t>
         </is>
       </c>
       <c r="C144" s="15" t="inlineStr">
@@ -10920,7 +10930,7 @@
       </c>
       <c r="D144" s="15" t="inlineStr">
         <is>
-          <t>Dijon métropole</t>
+          <t>[Perpignan]</t>
         </is>
       </c>
       <c r="E144" s="15" t="n">
@@ -10943,14 +10953,14 @@
       </c>
       <c r="I144" s="15" t="inlineStr">
         <is>
-          <t>19/02/2024</t>
+          <t>14/03/2024</t>
         </is>
       </c>
       <c r="J144" s="15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K144" s="15" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="L144" s="15" t="inlineStr"/>
       <c r="M144" s="15" t="inlineStr"/>
@@ -10967,22 +10977,22 @@
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14095</t>
+          <t>PDMDEP-14254</t>
         </is>
       </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
-          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
+          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>CC du Pays Sabolien</t>
+          <t>Dijon métropole</t>
         </is>
       </c>
       <c r="E145" s="12" t="n">
@@ -11000,19 +11010,19 @@
       </c>
       <c r="H145" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I145" s="12" t="inlineStr">
         <is>
-          <t>31/01/2024</t>
+          <t>19/02/2024</t>
         </is>
       </c>
       <c r="J145" s="12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K145" s="12" t="n">
-        <v>7.25</v>
+        <v>0.75</v>
       </c>
       <c r="L145" s="12" t="inlineStr"/>
       <c r="M145" s="12" t="inlineStr"/>
@@ -11029,22 +11039,22 @@
     <row r="146">
       <c r="A146" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-14095</t>
         </is>
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
         </is>
       </c>
       <c r="C146" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D146" s="15" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>CC du Pays Sabolien</t>
         </is>
       </c>
       <c r="E146" s="15" t="n">
@@ -11057,35 +11067,27 @@
       </c>
       <c r="G146" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H146" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I146" s="15" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>31/01/2024</t>
         </is>
       </c>
       <c r="J146" s="15" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K146" s="15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L146" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M146" s="15" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>7.25</v>
+      </c>
+      <c r="L146" s="15" t="inlineStr"/>
+      <c r="M146" s="15" t="inlineStr"/>
       <c r="N146" s="16" t="n">
         <v>0</v>
       </c>
@@ -11099,22 +11101,22 @@
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E147" s="12" t="n">
@@ -11130,20 +11132,32 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H147" s="12" t="inlineStr"/>
+      <c r="H147" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I147" s="12" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J147" s="12" t="n">
         <v>34</v>
       </c>
       <c r="K147" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L147" s="12" t="inlineStr"/>
-      <c r="M147" s="12" t="inlineStr"/>
+        <v>2.25</v>
+      </c>
+      <c r="L147" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M147" s="12" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N147" s="13" t="n">
         <v>0</v>
       </c>
@@ -11157,12 +11171,12 @@
     <row r="148">
       <c r="A148" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C148" s="15" t="inlineStr">
@@ -11172,7 +11186,7 @@
       </c>
       <c r="D148" s="15" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E148" s="15" t="n">
@@ -11185,24 +11199,20 @@
       </c>
       <c r="G148" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H148" s="15" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H148" s="15" t="inlineStr"/>
       <c r="I148" s="15" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J148" s="15" t="n">
         <v>34</v>
       </c>
       <c r="K148" s="15" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L148" s="15" t="inlineStr"/>
       <c r="M148" s="15" t="inlineStr"/>
@@ -11219,12 +11229,12 @@
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12443</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
@@ -11234,7 +11244,7 @@
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>CD79 - Deux Sèvres</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E149" s="12" t="n">
@@ -11257,14 +11267,14 @@
       </c>
       <c r="I149" s="12" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J149" s="12" t="n">
         <v>34</v>
       </c>
       <c r="K149" s="12" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L149" s="12" t="inlineStr"/>
       <c r="M149" s="12" t="inlineStr"/>
@@ -11281,28 +11291,26 @@
     <row r="150">
       <c r="A150" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12241</t>
+          <t>PDMDEP-12443</t>
         </is>
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
+          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C150" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D150" s="15" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe]</t>
-        </is>
-      </c>
-      <c r="E150" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement de Littéralis Expert</t>
-        </is>
+          <t>CD79 - Deux Sèvres</t>
+        </is>
+      </c>
+      <c r="E150" s="15" t="n">
+        <v/>
       </c>
       <c r="F150" s="15" t="inlineStr">
         <is>
@@ -11345,12 +11353,12 @@
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12241</t>
         </is>
       </c>
       <c r="B151" s="12" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr">
@@ -11360,12 +11368,12 @@
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>CD14</t>
+          <t>[SM Routes de Guadeloupe]</t>
         </is>
       </c>
       <c r="E151" s="12" t="inlineStr">
         <is>
-          <t>Modélisation spécifique</t>
+          <t>Déploiement de Littéralis Expert</t>
         </is>
       </c>
       <c r="F151" s="12" t="inlineStr">
@@ -11380,7 +11388,7 @@
       </c>
       <c r="H151" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I151" s="12" t="inlineStr">
@@ -11392,7 +11400,7 @@
         <v>34</v>
       </c>
       <c r="K151" s="12" t="n">
-        <v>8.75</v>
+        <v>0.5</v>
       </c>
       <c r="L151" s="12" t="inlineStr"/>
       <c r="M151" s="12" t="inlineStr"/>
@@ -11409,23 +11417,27 @@
     <row r="152">
       <c r="A152" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C152" s="15" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C152" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D152" s="15" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
+          <t>CD14</t>
         </is>
       </c>
       <c r="E152" s="15" t="inlineStr">
         <is>
-          <t>Déploiement Module AC</t>
+          <t>Modélisation spécifique</t>
         </is>
       </c>
       <c r="F152" s="15" t="inlineStr">
@@ -11440,19 +11452,19 @@
       </c>
       <c r="H152" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I152" s="15" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J152" s="15" t="n">
         <v>34</v>
       </c>
       <c r="K152" s="15" t="n">
-        <v>1.75</v>
+        <v>8.75</v>
       </c>
       <c r="L152" s="15" t="inlineStr"/>
       <c r="M152" s="15" t="inlineStr"/>
@@ -11469,21 +11481,25 @@
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr"/>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="E153" s="12" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E153" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F153" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11491,35 +11507,31 @@
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H153" s="12" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H153" s="12" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I153" s="12" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J153" s="12" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="K153" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L153" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M153" s="12" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>1.75</v>
+      </c>
+      <c r="L153" s="12" t="inlineStr"/>
+      <c r="M153" s="12" t="inlineStr"/>
       <c r="N153" s="13" t="n">
-        <v>510.6</v>
-      </c>
-      <c r="O153" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P153" s="13" t="n">
@@ -11529,18 +11541,18 @@
     <row r="154">
       <c r="A154" s="14" t="inlineStr">
         <is>
-          <t>PSC-1228</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MERLEVENEZ</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C154" s="15" t="inlineStr"/>
       <c r="D154" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MERLEVENEZ</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E154" s="15" t="inlineStr"/>
@@ -11557,61 +11569,121 @@
       <c r="H154" s="15" t="inlineStr"/>
       <c r="I154" s="15" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J154" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K154" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M154" s="15" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N154" s="16" t="n">
+        <v>510.6</v>
+      </c>
+      <c r="O154" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="11" t="inlineStr">
+        <is>
+          <t>PSC-1228</t>
+        </is>
+      </c>
+      <c r="B155" s="12" t="inlineStr">
+        <is>
+          <t>MAIRIE DE MERLEVENEZ</t>
+        </is>
+      </c>
+      <c r="C155" s="12" t="inlineStr"/>
+      <c r="D155" s="12" t="inlineStr">
+        <is>
+          <t>MAIRIE DE MERLEVENEZ</t>
+        </is>
+      </c>
+      <c r="E155" s="12" t="inlineStr"/>
+      <c r="F155" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G155" s="12" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H155" s="12" t="inlineStr"/>
+      <c r="I155" s="12" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="J154" s="15" t="n">
+      <c r="J155" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K154" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L154" s="15" t="inlineStr">
+      <c r="K155" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" s="12" t="inlineStr">
         <is>
           <t>PDMDEP-32829</t>
         </is>
       </c>
-      <c r="M154" s="15" t="inlineStr">
+      <c r="M155" s="12" t="inlineStr">
         <is>
           <t>00163534</t>
         </is>
       </c>
-      <c r="N154" s="16" t="n">
+      <c r="N155" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="O154" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P154" s="16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="18" t="inlineStr">
+      <c r="O155" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B155" s="18" t="inlineStr"/>
-      <c r="C155" s="18" t="inlineStr"/>
-      <c r="D155" s="18" t="inlineStr"/>
-      <c r="E155" s="18" t="inlineStr"/>
-      <c r="F155" s="18" t="inlineStr"/>
-      <c r="G155" s="18" t="inlineStr"/>
-      <c r="H155" s="18" t="inlineStr"/>
-      <c r="I155" s="18" t="inlineStr"/>
-      <c r="J155" s="18" t="inlineStr"/>
-      <c r="K155" s="18" t="inlineStr"/>
-      <c r="L155" s="18" t="inlineStr"/>
-      <c r="M155" s="18" t="inlineStr"/>
-      <c r="N155" s="19" t="n">
+      <c r="B156" s="18" t="inlineStr"/>
+      <c r="C156" s="18" t="inlineStr"/>
+      <c r="D156" s="18" t="inlineStr"/>
+      <c r="E156" s="18" t="inlineStr"/>
+      <c r="F156" s="18" t="inlineStr"/>
+      <c r="G156" s="18" t="inlineStr"/>
+      <c r="H156" s="18" t="inlineStr"/>
+      <c r="I156" s="18" t="inlineStr"/>
+      <c r="J156" s="18" t="inlineStr"/>
+      <c r="K156" s="18" t="inlineStr"/>
+      <c r="L156" s="18" t="inlineStr"/>
+      <c r="M156" s="18" t="inlineStr"/>
+      <c r="N156" s="19" t="n">
         <v>70028.95999999999</v>
       </c>
-      <c r="O155" s="19" t="n">
-        <v>11820.38</v>
-      </c>
-      <c r="P155" s="19" t="n">
-        <v>82.81999999999999</v>
+      <c r="O156" s="19" t="n">
+        <v>12225.38</v>
+      </c>
+      <c r="P156" s="19" t="n">
+        <v>85.65000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -11767,6 +11839,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId149"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId151"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jira_export_2026-07-09.xlsx
+++ b/jira_export_2026-07-09.xlsx
@@ -824,7 +824,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>255 h</t>
+          <t>271 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -838,7 +838,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>91.2%</t>
+          <t>96.9%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -909,7 +909,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>255</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -942,7 +942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P162"/>
+  <dimension ref="A1:P165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -3254,7 +3254,7 @@
         <v>1</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="12" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>4</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="L71" s="12" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>455</v>
       </c>
       <c r="P71" s="13" t="n">
-        <v>75.83</v>
+        <v>53.53</v>
       </c>
     </row>
     <row r="72">
@@ -8348,11 +8348,11 @@
         <v>8</v>
       </c>
       <c r="K106" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L106" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-28531</t>
         </is>
       </c>
       <c r="M106" s="15" t="inlineStr">
@@ -8364,7 +8364,7 @@
         <v>0</v>
       </c>
       <c r="O106" s="16" t="n">
-        <v>405</v>
+        <v>0</v>
       </c>
       <c r="P106" s="16" t="n">
         <v>0</v>
@@ -8373,30 +8373,32 @@
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E107" s="12" t="n">
-        <v/>
+          <t>Commune de CLAMART</t>
+        </is>
+      </c>
+      <c r="E107" s="12" t="inlineStr">
+        <is>
+          <t>Migration V2</t>
+        </is>
       </c>
       <c r="F107" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G107" s="12" t="inlineStr">
@@ -8406,12 +8408,12 @@
       </c>
       <c r="H107" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I107" s="12" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J107" s="12" t="n">
@@ -8422,33 +8424,33 @@
       </c>
       <c r="L107" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M107" s="12" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N107" s="13" t="n">
-        <v>2812.32</v>
-      </c>
-      <c r="O107" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O107" s="13" t="n">
+        <v>405</v>
       </c>
       <c r="P107" s="13" t="n">
-        <v>0</v>
+        <v>810</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">
@@ -8458,13 +8460,11 @@
       </c>
       <c r="D108" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E108" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E108" s="15" t="n">
+        <v/>
       </c>
       <c r="F108" s="15" t="inlineStr">
         <is>
@@ -8483,27 +8483,27 @@
       </c>
       <c r="I108" s="15" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J108" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K108" s="15" t="n">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M108" s="15" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N108" s="16" t="n">
-        <v>392.5</v>
+        <v>2812.32</v>
       </c>
       <c r="O108" s="17" t="n">
         <v>0</v>
@@ -8562,20 +8562,20 @@
         <v>8</v>
       </c>
       <c r="K109" s="12" t="n">
-        <v>0.85</v>
+        <v>1.05</v>
       </c>
       <c r="L109" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M109" s="12" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N109" s="13" t="n">
-        <v>1556.25</v>
+        <v>392.5</v>
       </c>
       <c r="O109" s="17" t="n">
         <v>0</v>
@@ -8634,20 +8634,20 @@
         <v>8</v>
       </c>
       <c r="K110" s="15" t="n">
-        <v>0.85</v>
+        <v>1.05</v>
       </c>
       <c r="L110" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M110" s="15" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N110" s="16" t="n">
-        <v>1790</v>
+        <v>1556.25</v>
       </c>
       <c r="O110" s="17" t="n">
         <v>0</v>
@@ -8706,22 +8706,22 @@
         <v>8</v>
       </c>
       <c r="K111" s="12" t="n">
-        <v>0.85</v>
+        <v>1.05</v>
       </c>
       <c r="L111" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M111" s="12" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N111" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O111" s="13" t="n">
+        <v>1790</v>
+      </c>
+      <c r="O111" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P111" s="13" t="n">
@@ -8778,16 +8778,16 @@
         <v>8</v>
       </c>
       <c r="K112" s="15" t="n">
-        <v>0.85</v>
+        <v>1.05</v>
       </c>
       <c r="L112" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M112" s="15" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N112" s="16" t="n">
@@ -8803,12 +8803,12 @@
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
@@ -8818,11 +8818,13 @@
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E113" s="12" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E113" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
@@ -8836,28 +8838,28 @@
       </c>
       <c r="H113" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I113" s="12" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J113" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K113" s="12" t="n">
-        <v>4.25</v>
+        <v>1.05</v>
       </c>
       <c r="L113" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M113" s="12" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N113" s="13" t="n">
@@ -8873,12 +8875,12 @@
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C114" s="15" t="inlineStr">
@@ -8888,7 +8890,7 @@
       </c>
       <c r="D114" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
         </is>
       </c>
       <c r="E114" s="15" t="n">
@@ -8906,34 +8908,34 @@
       </c>
       <c r="H114" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I114" s="15" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J114" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K114" s="15" t="n">
-        <v>2.5</v>
+        <v>4.25</v>
       </c>
       <c r="L114" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-27642</t>
         </is>
       </c>
       <c r="M114" s="15" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00143935</t>
         </is>
       </c>
       <c r="N114" s="16" t="n">
-        <v>732</v>
-      </c>
-      <c r="O114" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P114" s="16" t="n">
@@ -8943,12 +8945,12 @@
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26831</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
@@ -8958,38 +8960,52 @@
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>CD74</t>
-        </is>
-      </c>
-      <c r="E115" s="12" t="inlineStr">
-        <is>
-          <t>MAJ carto</t>
-        </is>
-      </c>
-      <c r="F115" s="12" t="inlineStr"/>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
+        </is>
+      </c>
+      <c r="E115" s="12" t="n">
+        <v/>
+      </c>
+      <c r="F115" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G115" s="12" t="inlineStr">
         <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="H115" s="12" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H115" s="12" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I115" s="12" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J115" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K115" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L115" s="12" t="inlineStr"/>
-      <c r="M115" s="12" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L115" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27557</t>
+        </is>
+      </c>
+      <c r="M115" s="12" t="inlineStr">
+        <is>
+          <t>00144532</t>
+        </is>
+      </c>
       <c r="N115" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O115" s="13" t="n">
+        <v>732</v>
+      </c>
+      <c r="O115" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P115" s="13" t="n">
@@ -8999,12 +9015,12 @@
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-26831</t>
         </is>
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
         </is>
       </c>
       <c r="C116" s="15" t="inlineStr">
@@ -9014,48 +9030,34 @@
       </c>
       <c r="D116" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
-        </is>
-      </c>
-      <c r="E116" s="15" t="n">
-        <v/>
-      </c>
-      <c r="F116" s="15" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+          <t>CD74</t>
+        </is>
+      </c>
+      <c r="E116" s="15" t="inlineStr">
+        <is>
+          <t>MAJ carto</t>
+        </is>
+      </c>
+      <c r="F116" s="15" t="inlineStr"/>
       <c r="G116" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H116" s="15" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="H116" s="15" t="inlineStr"/>
       <c r="I116" s="15" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="J116" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K116" s="15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L116" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-26814</t>
-        </is>
-      </c>
-      <c r="M116" s="15" t="inlineStr">
-        <is>
-          <t>00142941</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L116" s="15" t="inlineStr"/>
+      <c r="M116" s="15" t="inlineStr"/>
       <c r="N116" s="16" t="n">
         <v>0</v>
       </c>
@@ -9069,28 +9071,26 @@
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26782</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
-        </is>
-      </c>
-      <c r="E117" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement LiEx</t>
-        </is>
+          <t>VILLE DE VILLEJUIF</t>
+        </is>
+      </c>
+      <c r="E117" s="12" t="n">
+        <v/>
       </c>
       <c r="F117" s="12" t="inlineStr">
         <is>
@@ -9104,28 +9104,28 @@
       </c>
       <c r="H117" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I117" s="12" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J117" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K117" s="12" t="n">
-        <v>6.75</v>
+        <v>1.25</v>
       </c>
       <c r="L117" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-26783</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M117" s="12" t="inlineStr">
         <is>
-          <t>00142659</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N117" s="13" t="n">
@@ -9141,26 +9141,28 @@
     <row r="118">
       <c r="A118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-26782</t>
         </is>
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
         </is>
       </c>
       <c r="C118" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
-        </is>
-      </c>
-      <c r="E118" s="15" t="n">
-        <v/>
+          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
+        </is>
+      </c>
+      <c r="E118" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement LiEx</t>
+        </is>
       </c>
       <c r="F118" s="15" t="inlineStr">
         <is>
@@ -9179,29 +9181,29 @@
       </c>
       <c r="I118" s="15" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J118" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K118" s="15" t="n">
-        <v>1.5</v>
+        <v>8.75</v>
       </c>
       <c r="L118" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-26783</t>
         </is>
       </c>
       <c r="M118" s="15" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00142659</t>
         </is>
       </c>
       <c r="N118" s="16" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O118" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P118" s="16" t="n">
@@ -9211,12 +9213,12 @@
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24765</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>[COLOMBES] -  Litteralis - Interface Pastell</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
@@ -9226,7 +9228,7 @@
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE COLOMBES - DSIO</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E119" s="12" t="n">
@@ -9244,34 +9246,34 @@
       </c>
       <c r="H119" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I119" s="12" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J119" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K119" s="12" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="L119" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28062</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M119" s="12" t="inlineStr">
         <is>
-          <t>500768</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N119" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O119" s="13" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O119" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P119" s="13" t="n">
@@ -9281,22 +9283,22 @@
     <row r="120">
       <c r="A120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24426</t>
+          <t>PDMDEP-24765</t>
         </is>
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>[DRANCY] - Migration STD vers Exp</t>
+          <t>[COLOMBES] -  Litteralis - Interface Pastell</t>
         </is>
       </c>
       <c r="C120" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D120" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE DRANCY</t>
+          <t>VILLE DE COLOMBES - DSIO</t>
         </is>
       </c>
       <c r="E120" s="15" t="n">
@@ -9319,23 +9321,23 @@
       </c>
       <c r="I120" s="15" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="J120" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K120" s="15" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="L120" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27028</t>
+          <t>PDMDEP-28062</t>
         </is>
       </c>
       <c r="M120" s="15" t="inlineStr">
         <is>
-          <t>500950</t>
+          <t>500768</t>
         </is>
       </c>
       <c r="N120" s="16" t="n">
@@ -9351,12 +9353,12 @@
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
@@ -9366,7 +9368,7 @@
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
+          <t>VILLE DE DRANCY</t>
         </is>
       </c>
       <c r="E121" s="12" t="n">
@@ -9384,28 +9386,28 @@
       </c>
       <c r="H121" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I121" s="12" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J121" s="12" t="n">
         <v>10</v>
       </c>
       <c r="K121" s="12" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="L121" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27996</t>
+          <t>PDMDEP-27028</t>
         </is>
       </c>
       <c r="M121" s="12" t="inlineStr">
         <is>
-          <t>501219</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="N121" s="13" t="n">
@@ -9470,12 +9472,12 @@
       </c>
       <c r="L122" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27995</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M122" s="15" t="inlineStr">
         <is>
-          <t>501218</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N122" s="16" t="n">
@@ -9491,22 +9493,22 @@
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E123" s="12" t="n">
@@ -9529,29 +9531,29 @@
       </c>
       <c r="I123" s="12" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J123" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K123" s="12" t="n">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
       <c r="L123" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M123" s="12" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N123" s="13" t="n">
-        <v>2323</v>
-      </c>
-      <c r="O123" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P123" s="13" t="n">
@@ -9561,22 +9563,22 @@
     <row r="124">
       <c r="A124" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23486</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- AJOUT BALISE FILIEN</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C124" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D124" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E124" s="15" t="n">
@@ -9584,7 +9586,7 @@
       </c>
       <c r="F124" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G124" s="15" t="inlineStr">
@@ -9594,32 +9596,32 @@
       </c>
       <c r="H124" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I124" s="15" t="inlineStr">
         <is>
-          <t>25/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J124" s="15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K124" s="15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="L124" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27493</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M124" s="15" t="inlineStr">
         <is>
-          <t>495699</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N124" s="16" t="n">
-        <v>964.1</v>
+        <v>2323</v>
       </c>
       <c r="O124" s="17" t="n">
         <v>0</v>
@@ -9631,12 +9633,12 @@
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23484</t>
+          <t>PDMDEP-23486</t>
         </is>
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- AJOUT LIEU DE NAISSANCE DANS FILIEN</t>
+          <t>METROPOLE TOULON- AJOUT BALISE FILIEN</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
@@ -9680,19 +9682,19 @@
       </c>
       <c r="L125" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27494</t>
+          <t>PDMDEP-27493</t>
         </is>
       </c>
       <c r="M125" s="12" t="inlineStr">
         <is>
-          <t>495695</t>
+          <t>495699</t>
         </is>
       </c>
       <c r="N125" s="13" t="n">
-        <v>140.4</v>
+        <v>964.1</v>
       </c>
       <c r="O125" s="17" t="n">
-        <v>70.2</v>
+        <v>0</v>
       </c>
       <c r="P125" s="13" t="n">
         <v>0</v>
@@ -9701,22 +9703,22 @@
     <row r="126">
       <c r="A126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-23484</t>
         </is>
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>METROPOLE TOULON- AJOUT LIEU DE NAISSANCE DANS FILIEN</t>
         </is>
       </c>
       <c r="C126" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D126" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E126" s="15" t="n">
@@ -9724,7 +9726,7 @@
       </c>
       <c r="F126" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G126" s="15" t="inlineStr">
@@ -9734,35 +9736,35 @@
       </c>
       <c r="H126" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I126" s="15" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>25/07/2025</t>
         </is>
       </c>
       <c r="J126" s="15" t="n">
         <v>12</v>
       </c>
       <c r="K126" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L126" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-27494</t>
         </is>
       </c>
       <c r="M126" s="15" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>495695</t>
         </is>
       </c>
       <c r="N126" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O126" s="16" t="n">
-        <v>0</v>
+        <v>140.4</v>
+      </c>
+      <c r="O126" s="17" t="n">
+        <v>70.2</v>
       </c>
       <c r="P126" s="16" t="n">
         <v>0</v>
@@ -9771,22 +9773,22 @@
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-22996</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E127" s="12" t="n">
@@ -9804,28 +9806,28 @@
       </c>
       <c r="H127" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I127" s="12" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J127" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K127" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L127" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28051</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M127" s="12" t="inlineStr">
         <is>
-          <t>487190</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N127" s="13" t="n">
@@ -9841,22 +9843,22 @@
     <row r="128">
       <c r="A128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-22996</t>
         </is>
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
         </is>
       </c>
       <c r="C128" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D128" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E128" s="15" t="n">
@@ -9874,28 +9876,28 @@
       </c>
       <c r="H128" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I128" s="15" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="J128" s="15" t="n">
         <v>12</v>
       </c>
       <c r="K128" s="15" t="n">
-        <v>0.12</v>
+        <v>2</v>
       </c>
       <c r="L128" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-28051</t>
         </is>
       </c>
       <c r="M128" s="15" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>487190</t>
         </is>
       </c>
       <c r="N128" s="16" t="n">
@@ -9960,12 +9962,12 @@
       </c>
       <c r="L129" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M129" s="12" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N129" s="13" t="n">
@@ -9996,7 +9998,7 @@
       </c>
       <c r="D130" s="15" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E130" s="15" t="n">
@@ -10030,12 +10032,12 @@
       </c>
       <c r="L130" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M130" s="15" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N130" s="16" t="n">
@@ -10066,7 +10068,7 @@
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E131" s="12" t="n">
@@ -10100,12 +10102,12 @@
       </c>
       <c r="L131" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M131" s="12" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N131" s="13" t="n">
@@ -10121,12 +10123,12 @@
     <row r="132">
       <c r="A132" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22496</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - LITTERALIS Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C132" s="15" t="inlineStr">
@@ -10136,7 +10138,7 @@
       </c>
       <c r="D132" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E132" s="15" t="n">
@@ -10154,28 +10156,28 @@
       </c>
       <c r="H132" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I132" s="15" t="inlineStr">
         <is>
-          <t>23/06/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J132" s="15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K132" s="15" t="n">
-        <v>0.5</v>
+        <v>0.12</v>
       </c>
       <c r="L132" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27371</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M132" s="15" t="inlineStr">
         <is>
-          <t>481817</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N132" s="16" t="n">
@@ -10191,22 +10193,22 @@
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22496</t>
         </is>
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>[VILLEJUIF] - LITTERALIS Pastell</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E133" s="12" t="n">
@@ -10229,23 +10231,23 @@
       </c>
       <c r="I133" s="12" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>23/06/2025</t>
         </is>
       </c>
       <c r="J133" s="12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K133" s="12" t="n">
         <v>0.5</v>
       </c>
       <c r="L133" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27371</t>
         </is>
       </c>
       <c r="M133" s="12" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>481817</t>
         </is>
       </c>
       <c r="N133" s="13" t="n">
@@ -10261,22 +10263,22 @@
     <row r="134">
       <c r="A134" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21546</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C134" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D134" s="15" t="inlineStr">
         <is>
-          <t>VILLEURBANNE</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E134" s="15" t="n">
@@ -10284,7 +10286,7 @@
       </c>
       <c r="F134" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G134" s="15" t="inlineStr">
@@ -10299,29 +10301,29 @@
       </c>
       <c r="I134" s="15" t="inlineStr">
         <is>
-          <t>05/05/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J134" s="15" t="n">
         <v>14</v>
       </c>
       <c r="K134" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L134" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28038</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M134" s="15" t="inlineStr">
         <is>
-          <t>478867</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N134" s="16" t="n">
-        <v>482.72</v>
-      </c>
-      <c r="O134" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P134" s="16" t="n">
@@ -10331,22 +10333,22 @@
     <row r="135">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21546</t>
         </is>
       </c>
       <c r="B135" s="12" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>VILLEURBANNE</t>
         </is>
       </c>
       <c r="E135" s="12" t="n">
@@ -10354,7 +10356,7 @@
       </c>
       <c r="F135" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G135" s="12" t="inlineStr">
@@ -10364,34 +10366,34 @@
       </c>
       <c r="H135" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I135" s="12" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="J135" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K135" s="12" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L135" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-28038</t>
         </is>
       </c>
       <c r="M135" s="12" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>478867</t>
         </is>
       </c>
       <c r="N135" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O135" s="13" t="n">
+        <v>482.72</v>
+      </c>
+      <c r="O135" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P135" s="13" t="n">
@@ -10401,22 +10403,22 @@
     <row r="136">
       <c r="A136" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C136" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D136" s="15" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E136" s="15" t="n">
@@ -10434,34 +10436,34 @@
       </c>
       <c r="H136" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I136" s="15" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J136" s="15" t="n">
         <v>15</v>
       </c>
       <c r="K136" s="15" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L136" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M136" s="15" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N136" s="16" t="n">
-        <v>250</v>
-      </c>
-      <c r="O136" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P136" s="16" t="n">
@@ -10471,22 +10473,22 @@
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E137" s="12" t="n">
@@ -10509,27 +10511,27 @@
       </c>
       <c r="I137" s="12" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J137" s="12" t="n">
         <v>15</v>
       </c>
       <c r="K137" s="12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L137" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M137" s="12" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N137" s="13" t="n">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="O137" s="17" t="n">
         <v>0</v>
@@ -10541,22 +10543,22 @@
     <row r="138">
       <c r="A138" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C138" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D138" s="15" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E138" s="15" t="n">
@@ -10572,24 +10574,36 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H138" s="15" t="inlineStr"/>
+      <c r="H138" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I138" s="15" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J138" s="15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K138" s="15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L138" s="15" t="inlineStr"/>
-      <c r="M138" s="15" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L138" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M138" s="15" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
       <c r="N138" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O138" s="16" t="n">
+        <v>230</v>
+      </c>
+      <c r="O138" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P138" s="16" t="n">
@@ -10599,22 +10613,22 @@
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E139" s="12" t="n">
@@ -10630,32 +10644,20 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H139" s="12" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H139" s="12" t="inlineStr"/>
       <c r="I139" s="12" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J139" s="12" t="n">
         <v>16</v>
       </c>
       <c r="K139" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L139" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-28027</t>
-        </is>
-      </c>
-      <c r="M139" s="12" t="inlineStr">
-        <is>
-          <t>470688</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L139" s="12" t="inlineStr"/>
+      <c r="M139" s="12" t="inlineStr"/>
       <c r="N139" s="13" t="n">
         <v>0</v>
       </c>
@@ -10669,12 +10671,12 @@
     <row r="140">
       <c r="A140" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C140" s="15" t="inlineStr">
@@ -10684,7 +10686,7 @@
       </c>
       <c r="D140" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E140" s="15" t="n">
@@ -10702,28 +10704,28 @@
       </c>
       <c r="H140" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I140" s="15" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J140" s="15" t="n">
         <v>16</v>
       </c>
       <c r="K140" s="15" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L140" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M140" s="15" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N140" s="16" t="n">
@@ -10739,12 +10741,12 @@
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
@@ -10754,7 +10756,7 @@
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E141" s="12" t="n">
@@ -10772,28 +10774,28 @@
       </c>
       <c r="H141" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I141" s="12" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J141" s="12" t="n">
         <v>16</v>
       </c>
       <c r="K141" s="12" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L141" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M141" s="12" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N141" s="13" t="n">
@@ -10809,12 +10811,12 @@
     <row r="142">
       <c r="A142" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19385</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C142" s="15" t="inlineStr">
@@ -10824,7 +10826,7 @@
       </c>
       <c r="D142" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARCUEIL</t>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
         </is>
       </c>
       <c r="E142" s="15" t="n">
@@ -10847,23 +10849,23 @@
       </c>
       <c r="I142" s="15" t="inlineStr">
         <is>
-          <t>24/02/2025</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J142" s="15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K142" s="15" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L142" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27535</t>
+          <t>PDMDEP-27377</t>
         </is>
       </c>
       <c r="M142" s="15" t="inlineStr">
         <is>
-          <t>465345</t>
+          <t>478048</t>
         </is>
       </c>
       <c r="N142" s="16" t="n">
@@ -10879,12 +10881,12 @@
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-19385</t>
         </is>
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
@@ -10894,7 +10896,7 @@
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>COMMUNE D'ARCUEIL</t>
         </is>
       </c>
       <c r="E143" s="12" t="n">
@@ -10907,7 +10909,7 @@
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H143" s="12" t="inlineStr">
@@ -10917,17 +10919,25 @@
       </c>
       <c r="I143" s="12" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>24/02/2025</t>
         </is>
       </c>
       <c r="J143" s="12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K143" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L143" s="12" t="inlineStr"/>
-      <c r="M143" s="12" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L143" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27535</t>
+        </is>
+      </c>
+      <c r="M143" s="12" t="inlineStr">
+        <is>
+          <t>465345</t>
+        </is>
+      </c>
       <c r="N143" s="13" t="n">
         <v>0</v>
       </c>
@@ -10941,22 +10951,22 @@
     <row r="144">
       <c r="A144" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18212</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>[Besancon] Acquisition</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C144" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D144" s="15" t="inlineStr">
         <is>
-          <t>Besançon</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E144" s="15" t="n">
@@ -10964,7 +10974,7 @@
       </c>
       <c r="F144" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G144" s="15" t="inlineStr">
@@ -10974,7 +10984,7 @@
       </c>
       <c r="H144" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I144" s="15" t="inlineStr">
@@ -10986,7 +10996,7 @@
         <v>19</v>
       </c>
       <c r="K144" s="15" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="L144" s="15" t="inlineStr"/>
       <c r="M144" s="15" t="inlineStr"/>
@@ -11003,22 +11013,22 @@
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E145" s="12" t="n">
@@ -11026,44 +11036,36 @@
       </c>
       <c r="F145" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H145" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I145" s="12" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J145" s="12" t="n">
         <v>19</v>
       </c>
       <c r="K145" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L145" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M145" s="12" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="L145" s="12" t="inlineStr"/>
+      <c r="M145" s="12" t="inlineStr"/>
       <c r="N145" s="13" t="n">
-        <v>240</v>
-      </c>
-      <c r="O145" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O145" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P145" s="13" t="n">
@@ -11073,22 +11075,22 @@
     <row r="146">
       <c r="A146" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18212</t>
         </is>
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[Besancon] Acquisition</t>
         </is>
       </c>
       <c r="C146" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D146" s="15" t="inlineStr">
         <is>
-          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
+          <t>Besançon</t>
         </is>
       </c>
       <c r="E146" s="15" t="n">
@@ -11096,40 +11098,32 @@
       </c>
       <c r="F146" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G146" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H146" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I146" s="15" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J146" s="15" t="n">
         <v>19</v>
       </c>
       <c r="K146" s="15" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="L146" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-34362</t>
-        </is>
-      </c>
-      <c r="M146" s="15" t="inlineStr">
-        <is>
-          <t>458057</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L146" s="15" t="inlineStr"/>
+      <c r="M146" s="15" t="inlineStr"/>
       <c r="N146" s="16" t="n">
         <v>0</v>
       </c>
@@ -11143,22 +11137,22 @@
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E147" s="12" t="n">
@@ -11166,7 +11160,7 @@
       </c>
       <c r="F147" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G147" s="12" t="inlineStr">
@@ -11176,34 +11170,34 @@
       </c>
       <c r="H147" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I147" s="12" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J147" s="12" t="n">
         <v>19</v>
       </c>
       <c r="K147" s="12" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="L147" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28020</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M147" s="12" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N147" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O147" s="13" t="n">
+        <v>240</v>
+      </c>
+      <c r="O147" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P147" s="13" t="n">
@@ -11213,22 +11207,22 @@
     <row r="148">
       <c r="A148" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-16868</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>[Limoges] migration placier</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C148" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D148" s="15" t="inlineStr">
         <is>
-          <t>Limoges</t>
+          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
       <c r="E148" s="15" t="n">
@@ -11236,32 +11230,40 @@
       </c>
       <c r="F148" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G148" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H148" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I148" s="15" t="inlineStr">
         <is>
-          <t>26/09/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J148" s="15" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K148" s="15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L148" s="15" t="inlineStr"/>
-      <c r="M148" s="15" t="inlineStr"/>
+        <v>0.62</v>
+      </c>
+      <c r="L148" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34362</t>
+        </is>
+      </c>
+      <c r="M148" s="15" t="inlineStr">
+        <is>
+          <t>458057</t>
+        </is>
+      </c>
       <c r="N148" s="16" t="n">
         <v>0</v>
       </c>
@@ -11275,22 +11277,22 @@
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E149" s="12" t="n">
@@ -11303,7 +11305,7 @@
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H149" s="12" t="inlineStr">
@@ -11313,17 +11315,25 @@
       </c>
       <c r="I149" s="12" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J149" s="12" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="K149" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L149" s="12" t="inlineStr"/>
-      <c r="M149" s="12" t="inlineStr"/>
+        <v>0.62</v>
+      </c>
+      <c r="L149" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28020</t>
+        </is>
+      </c>
+      <c r="M149" s="12" t="inlineStr">
+        <is>
+          <t>458057</t>
+        </is>
+      </c>
       <c r="N149" s="13" t="n">
         <v>0</v>
       </c>
@@ -11337,22 +11347,22 @@
     <row r="150">
       <c r="A150" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14551</t>
+          <t>PDMDEP-16868</t>
         </is>
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>[Perpignan] Interface formulaire</t>
+          <t>[Limoges] migration placier</t>
         </is>
       </c>
       <c r="C150" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D150" s="15" t="inlineStr">
         <is>
-          <t>[Perpignan]</t>
+          <t>Limoges</t>
         </is>
       </c>
       <c r="E150" s="15" t="n">
@@ -11360,7 +11370,7 @@
       </c>
       <c r="F150" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G150" s="15" t="inlineStr">
@@ -11370,19 +11380,19 @@
       </c>
       <c r="H150" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I150" s="15" t="inlineStr">
         <is>
-          <t>14/03/2024</t>
+          <t>26/09/2024</t>
         </is>
       </c>
       <c r="J150" s="15" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K150" s="15" t="n">
-        <v>1.25</v>
+        <v>3.25</v>
       </c>
       <c r="L150" s="15" t="inlineStr"/>
       <c r="M150" s="15" t="inlineStr"/>
@@ -11399,22 +11409,22 @@
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14254</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B151" s="12" t="inlineStr">
         <is>
-          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>Dijon métropole</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E151" s="12" t="n">
@@ -11437,14 +11447,14 @@
       </c>
       <c r="I151" s="12" t="inlineStr">
         <is>
-          <t>19/02/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J151" s="12" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="K151" s="12" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L151" s="12" t="inlineStr"/>
       <c r="M151" s="12" t="inlineStr"/>
@@ -11461,22 +11471,22 @@
     <row r="152">
       <c r="A152" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14095</t>
+          <t>PDMDEP-14551</t>
         </is>
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
+          <t>[Perpignan] Interface formulaire</t>
         </is>
       </c>
       <c r="C152" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D152" s="15" t="inlineStr">
         <is>
-          <t>CC du Pays Sabolien</t>
+          <t>[Perpignan]</t>
         </is>
       </c>
       <c r="E152" s="15" t="n">
@@ -11494,19 +11504,19 @@
       </c>
       <c r="H152" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I152" s="15" t="inlineStr">
         <is>
-          <t>31/01/2024</t>
+          <t>14/03/2024</t>
         </is>
       </c>
       <c r="J152" s="15" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K152" s="15" t="n">
-        <v>7.25</v>
+        <v>1.25</v>
       </c>
       <c r="L152" s="15" t="inlineStr"/>
       <c r="M152" s="15" t="inlineStr"/>
@@ -11523,22 +11533,22 @@
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-14273</t>
         </is>
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[CD51 - MARNE] Modélisation, visa et Interface BG</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>CD Marne</t>
         </is>
       </c>
       <c r="E153" s="12" t="n">
@@ -11551,7 +11561,7 @@
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H153" s="12" t="inlineStr">
@@ -11561,25 +11571,17 @@
       </c>
       <c r="I153" s="12" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>20/02/2024</t>
         </is>
       </c>
       <c r="J153" s="12" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K153" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="L153" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M153" s="12" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L153" s="12" t="inlineStr"/>
+      <c r="M153" s="12" t="inlineStr"/>
       <c r="N153" s="13" t="n">
         <v>0</v>
       </c>
@@ -11593,22 +11595,22 @@
     <row r="154">
       <c r="A154" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-14254</t>
         </is>
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
         </is>
       </c>
       <c r="C154" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D154" s="15" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>Dijon métropole</t>
         </is>
       </c>
       <c r="E154" s="15" t="n">
@@ -11621,20 +11623,24 @@
       </c>
       <c r="G154" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H154" s="15" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H154" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I154" s="15" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>19/02/2024</t>
         </is>
       </c>
       <c r="J154" s="15" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K154" s="15" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L154" s="15" t="inlineStr"/>
       <c r="M154" s="15" t="inlineStr"/>
@@ -11651,12 +11657,12 @@
     <row r="155">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-14095</t>
         </is>
       </c>
       <c r="B155" s="12" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
         </is>
       </c>
       <c r="C155" s="12" t="inlineStr">
@@ -11666,7 +11672,7 @@
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CC du Pays Sabolien</t>
         </is>
       </c>
       <c r="E155" s="12" t="n">
@@ -11689,14 +11695,14 @@
       </c>
       <c r="I155" s="12" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>31/01/2024</t>
         </is>
       </c>
       <c r="J155" s="12" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K155" s="12" t="n">
-        <v>1</v>
+        <v>7.25</v>
       </c>
       <c r="L155" s="12" t="inlineStr"/>
       <c r="M155" s="12" t="inlineStr"/>
@@ -11713,22 +11719,22 @@
     <row r="156">
       <c r="A156" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12443</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C156" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D156" s="15" t="inlineStr">
         <is>
-          <t>CD79 - Deux Sèvres</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E156" s="15" t="n">
@@ -11741,27 +11747,35 @@
       </c>
       <c r="G156" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H156" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I156" s="15" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J156" s="15" t="n">
         <v>34</v>
       </c>
       <c r="K156" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L156" s="15" t="inlineStr"/>
-      <c r="M156" s="15" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="L156" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M156" s="15" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N156" s="16" t="n">
         <v>0</v>
       </c>
@@ -11775,28 +11789,26 @@
     <row r="157">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12241</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B157" s="12" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe]</t>
-        </is>
-      </c>
-      <c r="E157" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement de Littéralis Expert</t>
-        </is>
+          <t>CD 56 MORBIHAN</t>
+        </is>
+      </c>
+      <c r="E157" s="12" t="n">
+        <v/>
       </c>
       <c r="F157" s="12" t="inlineStr">
         <is>
@@ -11805,17 +11817,13 @@
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H157" s="12" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H157" s="12" t="inlineStr"/>
       <c r="I157" s="12" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J157" s="12" t="n">
@@ -11839,28 +11847,26 @@
     <row r="158">
       <c r="A158" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C158" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D158" s="15" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E158" s="15" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E158" s="15" t="n">
+        <v/>
       </c>
       <c r="F158" s="15" t="inlineStr">
         <is>
@@ -11874,21 +11880,25 @@
       </c>
       <c r="H158" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I158" s="15" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J158" s="15" t="n">
         <v>34</v>
       </c>
       <c r="K158" s="15" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="L158" s="15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L158" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
       <c r="M158" s="15" t="inlineStr"/>
       <c r="N158" s="16" t="n">
         <v>0</v>
@@ -11903,24 +11913,26 @@
     <row r="159">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12443</t>
         </is>
       </c>
       <c r="B159" s="12" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C159" s="12" t="inlineStr"/>
+          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C159" s="12" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E159" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>CD79 - Deux Sèvres</t>
+        </is>
+      </c>
+      <c r="E159" s="12" t="n">
+        <v/>
       </c>
       <c r="F159" s="12" t="inlineStr">
         <is>
@@ -11939,14 +11951,14 @@
       </c>
       <c r="I159" s="12" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J159" s="12" t="n">
         <v>34</v>
       </c>
       <c r="K159" s="12" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="L159" s="12" t="inlineStr"/>
       <c r="M159" s="12" t="inlineStr"/>
@@ -11963,21 +11975,29 @@
     <row r="160">
       <c r="A160" s="14" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PDMDEP-12241</t>
         </is>
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="C160" s="15" t="inlineStr"/>
+          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C160" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D160" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="E160" s="15" t="inlineStr"/>
+          <t>[SM Routes de Guadeloupe]</t>
+        </is>
+      </c>
+      <c r="E160" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement de Littéralis Expert</t>
+        </is>
+      </c>
       <c r="F160" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11985,35 +12005,31 @@
       </c>
       <c r="G160" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H160" s="15" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H160" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I160" s="15" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J160" s="15" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="K160" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L160" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M160" s="15" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L160" s="15" t="inlineStr"/>
+      <c r="M160" s="15" t="inlineStr"/>
       <c r="N160" s="16" t="n">
-        <v>510.6</v>
-      </c>
-      <c r="O160" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O160" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P160" s="16" t="n">
@@ -12023,89 +12039,273 @@
     <row r="161">
       <c r="A161" s="11" t="inlineStr">
         <is>
+          <t>PDMDEP-12222</t>
+        </is>
+      </c>
+      <c r="B161" s="12" t="inlineStr">
+        <is>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C161" s="12" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D161" s="12" t="inlineStr">
+        <is>
+          <t>CD14</t>
+        </is>
+      </c>
+      <c r="E161" s="12" t="inlineStr">
+        <is>
+          <t>Modélisation spécifique</t>
+        </is>
+      </c>
+      <c r="F161" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G161" s="12" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H161" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I161" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2023</t>
+        </is>
+      </c>
+      <c r="J161" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="K161" s="12" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="L161" s="12" t="inlineStr"/>
+      <c r="M161" s="12" t="inlineStr"/>
+      <c r="N161" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O161" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P161" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-11477</t>
+        </is>
+      </c>
+      <c r="B162" s="15" t="inlineStr">
+        <is>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C162" s="15" t="inlineStr"/>
+      <c r="D162" s="15" t="inlineStr">
+        <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E162" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
+      <c r="F162" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G162" s="15" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H162" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I162" s="15" t="inlineStr">
+        <is>
+          <t>03/09/2023</t>
+        </is>
+      </c>
+      <c r="J162" s="15" t="n">
+        <v>34</v>
+      </c>
+      <c r="K162" s="15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="L162" s="15" t="inlineStr"/>
+      <c r="M162" s="15" t="inlineStr"/>
+      <c r="N162" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O162" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="11" t="inlineStr">
+        <is>
+          <t>PSC-1270</t>
+        </is>
+      </c>
+      <c r="B163" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="C163" s="12" t="inlineStr"/>
+      <c r="D163" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="E163" s="12" t="inlineStr"/>
+      <c r="F163" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G163" s="12" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H163" s="12" t="inlineStr"/>
+      <c r="I163" s="12" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J163" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K163" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L163" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M163" s="12" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N163" s="13" t="n">
+        <v>510.6</v>
+      </c>
+      <c r="O163" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="14" t="inlineStr">
+        <is>
           <t>PSC-1228</t>
         </is>
       </c>
-      <c r="B161" s="12" t="inlineStr">
+      <c r="B164" s="15" t="inlineStr">
         <is>
           <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
-      <c r="C161" s="12" t="inlineStr"/>
-      <c r="D161" s="12" t="inlineStr">
+      <c r="C164" s="15" t="inlineStr"/>
+      <c r="D164" s="15" t="inlineStr">
         <is>
           <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
-      <c r="E161" s="12" t="inlineStr"/>
-      <c r="F161" s="12" t="inlineStr">
+      <c r="E164" s="15" t="inlineStr"/>
+      <c r="F164" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G161" s="12" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H161" s="12" t="inlineStr"/>
-      <c r="I161" s="12" t="inlineStr">
+      <c r="G164" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H164" s="15" t="inlineStr"/>
+      <c r="I164" s="15" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="J161" s="12" t="n">
+      <c r="J164" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="K161" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L161" s="12" t="inlineStr">
+      <c r="K164" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L164" s="15" t="inlineStr">
         <is>
           <t>PDMDEP-32829</t>
         </is>
       </c>
-      <c r="M161" s="12" t="inlineStr">
+      <c r="M164" s="15" t="inlineStr">
         <is>
           <t>00163534</t>
         </is>
       </c>
-      <c r="N161" s="13" t="n">
+      <c r="N164" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="O161" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P161" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="18" t="inlineStr">
+      <c r="O164" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B162" s="18" t="inlineStr"/>
-      <c r="C162" s="18" t="inlineStr"/>
-      <c r="D162" s="18" t="inlineStr"/>
-      <c r="E162" s="18" t="inlineStr"/>
-      <c r="F162" s="18" t="inlineStr"/>
-      <c r="G162" s="18" t="inlineStr"/>
-      <c r="H162" s="18" t="inlineStr"/>
-      <c r="I162" s="18" t="inlineStr"/>
-      <c r="J162" s="18" t="inlineStr"/>
-      <c r="K162" s="18" t="inlineStr"/>
-      <c r="L162" s="18" t="inlineStr"/>
-      <c r="M162" s="18" t="inlineStr"/>
-      <c r="N162" s="19" t="n">
+      <c r="B165" s="18" t="inlineStr"/>
+      <c r="C165" s="18" t="inlineStr"/>
+      <c r="D165" s="18" t="inlineStr"/>
+      <c r="E165" s="18" t="inlineStr"/>
+      <c r="F165" s="18" t="inlineStr"/>
+      <c r="G165" s="18" t="inlineStr"/>
+      <c r="H165" s="18" t="inlineStr"/>
+      <c r="I165" s="18" t="inlineStr"/>
+      <c r="J165" s="18" t="inlineStr"/>
+      <c r="K165" s="18" t="inlineStr"/>
+      <c r="L165" s="18" t="inlineStr"/>
+      <c r="M165" s="18" t="inlineStr"/>
+      <c r="N165" s="19" t="n">
         <v>70028.95999999999</v>
       </c>
-      <c r="O162" s="19" t="n">
+      <c r="O165" s="19" t="n">
         <v>12225.38</v>
       </c>
-      <c r="P162" s="19" t="n">
-        <v>77.51000000000001</v>
+      <c r="P165" s="19" t="n">
+        <v>72.89</v>
       </c>
     </row>
   </sheetData>
@@ -12268,6 +12468,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A159" r:id="rId155"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A160" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId160"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12842,26 +13045,26 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>0.75</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>116.75</v>
+        <v>124.75</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>486.15</v>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>25.7%</t>
         </is>
       </c>
     </row>
@@ -12872,7 +13075,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>4.75</v>
@@ -12881,17 +13084,17 @@
         <v>0.5</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>39.25</v>
+        <v>41.25</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="G6" s="12" t="n">
         <v>263.34</v>
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>15.7%</t>
         </is>
       </c>
     </row>
@@ -12903,7 +13106,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>57.33</v>
+        <v>61.83</v>
       </c>
     </row>
   </sheetData>
@@ -13067,7 +13270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -13091,7 +13294,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 5 commande(s)</t>
+          <t>Épics créées ce mois — 6 commande(s)</t>
         </is>
       </c>
     </row>
@@ -13146,22 +13349,22 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34481</t>
+          <t>PDMDEP-34527</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34475</t>
+          <t>PDMDEP-34521</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>Mairie de Pontcharra</t>
+          <t>COMMUNE DE FRONTON</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -13171,7 +13374,7 @@
       </c>
       <c r="F5" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -13181,22 +13384,22 @@
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>00172611</t>
+          <t>00173007</t>
         </is>
       </c>
       <c r="I5" s="26" t="n">
-        <v>1050</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34466</t>
+          <t>PDMDEP-34481</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34457</t>
+          <t>PDMDEP-34475</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -13206,7 +13409,7 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Commune de La Flèche</t>
+          <t>Mairie de Pontcharra</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
@@ -13226,32 +13429,32 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>00172594</t>
+          <t>00172611</t>
         </is>
       </c>
       <c r="I6" s="27" t="n">
-        <v>4475</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34420</t>
+          <t>PDMDEP-34466</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34411</t>
+          <t>PDMDEP-34457</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MAIZIERES LES METZ</t>
+          <t>Commune de La Flèche</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -13271,32 +13474,32 @@
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>00172317</t>
+          <t>00172594</t>
         </is>
       </c>
       <c r="I7" s="26" t="n">
-        <v>2035</v>
+        <v>4475</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34396</t>
+          <t>PDMDEP-34420</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34390</t>
+          <t>PDMDEP-34411</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Commune Le THOR</t>
+          <t>MAIRIE DE MAIZIERES LES METZ</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
@@ -13306,7 +13509,7 @@
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
@@ -13316,83 +13519,107 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>00171793</t>
+          <t>00172317</t>
         </is>
       </c>
       <c r="I8" s="27" t="n">
-        <v>250</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
+          <t>PDMDEP-34396</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34390</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>Commune Le THOR</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>00171793</t>
+        </is>
+      </c>
+      <c r="I9" s="26" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
           <t>PDMDEP-34499</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>PDMDEP-34495</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>COMMUNE DE CLICHY</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G9" s="15" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H9" s="15" t="inlineStr">
+      <c r="H10" s="12" t="inlineStr">
         <is>
           <t>00172678</t>
         </is>
       </c>
-      <c r="I9" s="26" t="n">
+      <c r="I10" s="27" t="n">
         <v>4300</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="18" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="n"/>
-      <c r="C10" s="18" t="n"/>
-      <c r="D10" s="18" t="n"/>
-      <c r="E10" s="18" t="n"/>
-      <c r="F10" s="18" t="n"/>
-      <c r="G10" s="18" t="n"/>
-      <c r="H10" s="18" t="inlineStr">
-        <is>
-          <t>5 commande(s)</t>
-        </is>
-      </c>
-      <c r="I10" s="25" t="n">
-        <v>12110</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="18" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B11" s="18" t="n"/>
@@ -13403,17 +13630,17 @@
       <c r="G11" s="18" t="n"/>
       <c r="H11" s="18" t="inlineStr">
         <is>
-          <t>1 commande(s)</t>
+          <t>6 commande(s)</t>
         </is>
       </c>
       <c r="I11" s="25" t="n">
-        <v>4300</v>
+        <v>12110</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B12" s="18" t="n"/>
@@ -13424,10 +13651,31 @@
       <c r="G12" s="18" t="n"/>
       <c r="H12" s="18" t="inlineStr">
         <is>
-          <t>4 commande(s)</t>
+          <t>1 commande(s)</t>
         </is>
       </c>
       <c r="I12" s="25" t="n">
+        <v>4300</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="n"/>
+      <c r="C13" s="18" t="n"/>
+      <c r="D13" s="18" t="n"/>
+      <c r="E13" s="18" t="n"/>
+      <c r="F13" s="18" t="n"/>
+      <c r="G13" s="18" t="n"/>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>5 commande(s)</t>
+        </is>
+      </c>
+      <c r="I13" s="25" t="n">
         <v>7810</v>
       </c>
     </row>
